--- a/Questions/July 5 2026/julia_july5_answers.xlsx
+++ b/Questions/July 5 2026/julia_july5_answers.xlsx
@@ -62,6 +62,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
@@ -82,12 +88,6 @@
       <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Consolas"/>
@@ -124,6 +124,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
@@ -140,16 +150,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00375623"/>
       </patternFill>
     </fill>
     <fill>
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -220,46 +220,49 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -271,37 +274,37 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -313,13 +316,13 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -688,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -719,7 +722,7 @@
     <row r="5" ht="58" customHeight="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Julia sent five follow-up questions (chat, 4 Jul) plus a request to trace real patients from raw claims through to their final assigned line of therapy (LOT). This single workbook answers all of them and adds the Optum medical-vs-pharmacy coverage validation you asked for. One tab per question, plus worked patient journeys.</t>
+          <t>Julia sent five follow-up questions (see Questions/July 5 2026) plus a request to trace patients from raw claims through to their final assigned line of therapy (LOT). This single workbook answers all of them and adds the Optum medical-vs-pharmacy coverage validation you asked for. One tab per question, plus worked patient journeys.</t>
         </is>
       </c>
     </row>
@@ -729,124 +732,144 @@
     <row r="7" ht="20" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ▶  IMPORTANT — how to read the numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="104" customHeight="1">
+          <t xml:space="preserve">  ▶  ONE-LINE COVER NOTE for whoever forwards this to Julia</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>The patient-level counts Julia asks for (how many POMA-1L patients have an SCT, another cancer, a clinical trial, etc.) live in the Databricks warehouse (hive_metastore / Optum CDM), which this repository cannot reach. So this workbook gives, for each question: (1) the precise answer/interpretation grounded in the protocol + program spec, (2) the exact, ready-to-run query that produces the count, and (3) the honest limits. Where a query already exists in the codebase it is cited. The patient-journey tabs ARE fully worked end-to-end — they were produced by running the project's LOT engine on illustrative synthetic patients, so they show the exact journey format and the algorithm's real behaviour.</t>
+          <t>The patient journeys here are SYNTHETIC, rule-faithful examples that show the complete raw-claims → MAP → LOT journey; the actual patient examples and the requested counts require running the included SQL against the Databricks warehouse. Everything else (the Optum coverage validation, the method, and the queries) is final.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="B10" s="3" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  IMPORTANT — how to read the numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="104" customHeight="1">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>The patient-level counts Julia asks for (how many POMA-1L patients have an SCT, another cancer, a clinical trial, etc.) live in the Databricks warehouse (hive_metastore / Optum CDM), which this repository cannot reach. So this workbook gives, for each question: (1) the precise answer/interpretation grounded in the protocol + program spec, (2) the exact, ready-to-run query that produces the count, and (3) the honest limits. Where a query already exists in the codebase it is cited. The patient-journey tabs ARE fully worked end-to-end — they were produced by running the project's LOT engine on illustrative synthetic patients, so they show the exact journey format and the algorithm's real behaviour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>The five questions (Julia, 4 Jul 2026)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="B11" s="8" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>1.  Trace a few different types of patients from raw claims to final assigned LOT — a mix of LOT1-5, SCT or CAR-T, and consolidation therapy around CAR-T.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="B12" s="8" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>2.  For patients receiving POMA in 1L: are there patients who also receive SCT or CAR-T in the cohort? Would indicate they are not treatment-naive.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="8" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>3.  Is POMA highly associated with evidence of any of the permissible cancers we allow to occur in baseline?</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="B14" s="8" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>4.  Do POMA patients have evidence of clinical-trial participation?</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="B15" s="8" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>5.  Do POMA patients have continuous PHARMACY benefit (not just medical)? These cases could hide prior LEN/THAL first-line exposure outside observable pharmacy claims.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Tabs in this workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>•  Answers at a glance — one-line answer + data status for every question.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>•  Optum coverage (validation) — the medical-vs-pharmacy question, validated against the data dictionary and program spec.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>•  Q1 journeys — guide — what the traces show + how to pull the same trace for a real patient.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>•  Q1 raw claims / Q1 MAP segments / Q1 LOT assignment — the full raw-claims → MAP → LOT chain for six archetype patients.</t>
+          <t>•  Answers at a glance — one-line answer + data status for every question.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>•  Q2 POMA &amp; SCT/CAR-T  •  Q3 POMA &amp; other cancers  •  Q4 POMA &amp; clinical trials  •  Q5 POMA &amp; pharmacy benefit.</t>
+          <t>•  Optum coverage (validation) — the medical-vs-pharmacy question, validated against the data dictionary and program spec.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>•  Q1 journeys — guide — what the traces show + how to pull the same trace for a real patient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>•  Q1 raw claims / Q1 MAP segments / Q1 LOT assignment — the full raw-claims → MAP → LOT chain for six archetype patients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>•  Q2 POMA &amp; SCT/CAR-T  •  Q3 POMA &amp; other cancers  •  Q4 POMA &amp; clinical trials  •  Q5 POMA &amp; pharmacy benefit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
           <t>•  Method &amp; data sources — provenance, the LOT engine, and every file cited.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="25">
     <mergeCell ref="B9"/>
     <mergeCell ref="B15"/>
     <mergeCell ref="B6"/>
+    <mergeCell ref="B24"/>
     <mergeCell ref="B20"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="B4"/>
+    <mergeCell ref="B26"/>
     <mergeCell ref="B7"/>
+    <mergeCell ref="B25"/>
     <mergeCell ref="B16"/>
     <mergeCell ref="B22"/>
     <mergeCell ref="A2:B2"/>
@@ -895,48 +918,48 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Short answer</t>
         </is>
       </c>
     </row>
     <row r="5" ht="64" customHeight="1">
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Answerable in the ELIG_COH build, and already coded. Like other-cancer, clinical-trial participation (Exclusion Criterion 9) is NOT applied in ELIG_COH, so those patients are retained and their CLINTRIAL_BASELINE / CLINTRIAL_FOLLOWUP flags are available. apr_30_2026/lot1_studyteam_qs.R computes these among POMA-1L (its question Q1c).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="6" customHeight="1">
-      <c r="B6" s="35" t="inlineStr"/>
+      <c r="B6" s="36" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Why Julia is asking</t>
         </is>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1">
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Clinical-trial participation is a plausible explanation for an apparent POMA-1L: a patient could have received an unobserved investigational first-line therapy on trial (study drug not billed through normal claims), making the first CLAIMS-visible regimen look like line 1 when it is really a later line. A high trial rate among POMA-1L would support the 'not truly first-line / not treatment-naive' hypothesis and would pair with the Q2 transplant signal.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1">
-      <c r="B9" s="35" t="inlineStr"/>
+      <c r="B9" s="36" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Query (Databricks) — clinical-trial evidence among POMA-1L</t>
         </is>
       </c>
     </row>
     <row r="11" ht="216" customHeight="1">
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>WITH poma1l AS (
   SELECT DISTINCT cast(PATID AS string) PATID FROM &lt;work&gt;.LOT_LONG
@@ -949,25 +972,25 @@
   JOIN &lt;work&gt;.ELIG_COH_FINAL   e ON e.PATID=a.PATID AND e.INDEX_DATE=a.INDEX_DATE
 )
 SELECT count(*)                                                       AS poma_1l_pts,
-       sum(f.CLINTRIAL_BASELINE)                                      AS trial_baseline,
-       sum(f.CLINTRIAL_FOLLOWUP)                                      AS trial_followup,
-       sum(CASE WHEN f.CLINTRIAL_BASELINE=1 OR f.CLINTRIAL_FOLLOWUP=1 THEN 1 END) AS trial_any
+       sum(coalesce(f.CLINTRIAL_BASELINE,0))                          AS trial_baseline,
+       sum(coalesce(f.CLINTRIAL_FOLLOWUP,0))                          AS trial_followup,
+       sum(CASE WHEN f.CLINTRIAL_BASELINE=1 OR f.CLINTRIAL_FOLLOWUP=1 THEN 1 ELSE 0 END) AS trial_any
 FROM poma1l JOIN f USING (PATID);</t>
         </is>
       </c>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="B12" s="35" t="inlineStr"/>
+      <c r="B12" s="36" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Honest limits</t>
         </is>
       </c>
     </row>
     <row r="14" ht="64" customHeight="1">
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Clinical-trial participation in claims is itself imperfectly captured (trial dx/procedure/revenue codes, spec Tab 46) — an on-trial patient with the study drug fully masked may carry no trial code at all, so this is a lower bound. Report it alongside the Q2 transplant breakdown and the Q5 look-back for a fuller non-naive picture.</t>
         </is>
@@ -1000,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1022,89 +1045,104 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Short answer (see the 'Optum coverage' tab for the full validation)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="106" customHeight="1">
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>The premise that a patient could have medical-but-not-pharmacy coverage does not really apply to Optum: membership requires BOTH benefits, so every cohort patient has pharmacy coverage and oral LEN/THAL fills are visible as NDC claims (given those NDCs are in the study's Tab 41 code list). Combined with the baseline-therapy exclusion (Criterion 3, which already screens medical AND pharmacy claims for prior MM therapy), a delivered POMA-1L patient cannot be hiding an observable-window oral first-line agent. The only genuine gap is exposure BEFORE the 6-month look-back.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="6" customHeight="1">
-      <c r="B6" s="35" t="inlineStr"/>
+      <c r="B6" s="36" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Confirmatory query — pharmacy-benefit continuity + extended LEN/THAL look-back</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Even though Optum guarantees pharmacy benefit, you can prove it per-patient and push the look-back as far back as each patient's enrollment allows, to quantify the true residual:</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="328" customHeight="1">
-      <c r="B9" s="23" t="inlineStr">
+    <row r="9" ht="78" customHeight="1">
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>Table names below follow the repo's config_prompts.R: CDM sources are read via cdm_src(), which resolves to the quarterly tables when USE_QUARTERLY_TABLES=TRUE — e.g. cdm_src('rx') → &lt;cdm&gt;.t_rx_2025q2, cdm_src('member_cont_enrollment') → &lt;cdm&gt;.t_member_cont_enrollment_2025q2. LEN/THAL NDCs come from the study's own therapy code list (cl_mma_codelist.csv), the same source the pipeline's mm_therapy_codes view uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="426" customHeight="1">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>WITH poma1l AS (
   SELECT DISTINCT cast(PATID AS string) PATID FROM &lt;work&gt;.LOT_LONG
   WHERE LOT_NUM=1 AND array_contains(split(LOT_BASE_MEDS,' '),'POMA')
 ),
 idx AS (SELECT cast(PATID AS string) PATID, INDEX_DATE FROM &lt;work&gt;.ELIG_COH_FINAL),
+-- LEN/THAL NDCs from the study MM-therapy codelist (cl_mma_codelist), 11-digit normalized
+len_thal AS (
+  SELECT DISTINCT lpad(regexp_replace(CL_CODE,'[^0-9]',''),11,'0') AS ndc
+  FROM &lt;ref&gt;.cl_mma_codelist
+  WHERE upper(CL_CODE_TYPE)='NDC' AND upper(CL_MED_ABBR) IN ('LENA','THAL')
+),
 -- longest continuous pre-index enrollment span per patient (proxy for observable history)
 enr AS (
-  SELECT cast(PATID AS string) PATID,
-         min(ELIGEFF) first_cov, max(ELIGEND) last_cov
-  FROM &lt;cdm&gt;.t_member_continuous_enrollment GROUP BY PATID
+  SELECT cast(PATID AS string) PATID, min(ELIGEFF) first_cov, max(ELIGEND) last_cov
+  FROM &lt;cdm&gt;.t_member_cont_enrollment_2025q2 GROUP BY PATID     -- = cdm_src('member_cont_enrollment')
 ),
--- ANY LEN/THAL pharmacy fill BEFORE index but before the 6-month baseline window
+-- earliest LEN/THAL pharmacy fill (any time observable)
 early_oral AS (
-  SELECT cast(r.PATID AS string) PATID, min(r.FILL_DT) first_len_thal
-  FROM &lt;cdm&gt;.t_rx r JOIN &lt;codelist&gt;.len_thal_ndc c ON r.NDC=c.NDC
+  SELECT cast(r.PATID AS string) PATID, min(cast(r.FILL_DT AS date)) first_len_thal
+  FROM &lt;cdm&gt;.t_rx_2025q2 r                                        -- = cdm_src('rx')
+  JOIN len_thal t
+    ON lpad(regexp_replace(coalesce(cast(r.NDC AS string),''),'[^0-9]',''),11,'0') = t.ndc
   GROUP BY r.PATID
 )
-SELECT count(*)                                                        AS poma_1l_pts,
-       sum(CASE WHEN datediff(i.INDEX_DATE, e.first_cov) &gt; 183 THEN 1 END) AS obs_history_gt_6mo,
-       sum(CASE WHEN o.first_len_thal &lt; date_sub(i.INDEX_DATE,183) THEN 1 END) AS early_len_thal_pre_baseline
+SELECT count(*)                                                            AS poma_1l_pts,
+       sum(CASE WHEN datediff(i.INDEX_DATE, e.first_cov) &gt; 183 THEN 1 ELSE 0 END) AS obs_history_gt_6mo,
+       sum(CASE WHEN o.first_len_thal &lt; date_sub(i.INDEX_DATE,183) THEN 1 ELSE 0 END) AS early_len_thal_pre_baseline
 FROM poma1l p JOIN idx i USING (PATID)
              JOIN enr e USING (PATID)
              LEFT JOIN early_oral o USING (PATID);</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="6" customHeight="1">
-      <c r="B10" s="35" t="inlineStr"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="B11" s="34" t="inlineStr">
+    <row r="11" ht="6" customHeight="1">
+      <c r="B11" s="36" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Honest limits</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="78" customHeight="1">
-      <c r="B12" s="13" t="inlineStr">
+    <row r="13" ht="78" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>'early_len_thal_pre_baseline' finds prior oral exposure that sits before the 6-month exclusion window — that is exactly the residual blind spot, and it is measurable. What remains truly unobservable is any therapy before a patient's first Optum enrollment date; report obs_history_gt_6mo so Julia can see how many POMA-1L patients even have enough pre-index history for the look-back to be meaningful.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="B8"/>
     <mergeCell ref="B4"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B9"/>
     <mergeCell ref="B12"/>
+    <mergeCell ref="B13"/>
     <mergeCell ref="B7"/>
     <mergeCell ref="B11"/>
     <mergeCell ref="B6"/>
@@ -1123,7 +1161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1131,7 +1169,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>Method &amp; data sources</t>
         </is>
@@ -1145,7 +1183,7 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Data access</t>
         </is>
@@ -1162,7 +1200,7 @@
       <c r="B6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>The LOT engine used for the Q1 journeys</t>
         </is>
@@ -1179,73 +1217,81 @@
       <c r="B9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>Files cited in this workbook</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="25" t="inlineStr"/>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr"/>
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>[Optum coverage / Q5]  docs/Part 3/Program Spec/studypoppage_validated.csv — DATA_SOURCE, CE_b, Criterion 3 (MM_bl_agents), Criterion 5</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="25" t="inlineStr"/>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr"/>
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>[Optum coverage]  Apr 18 2026/Optum - Business Rules/optum business rules.pdf — member enrollment &amp; continuous enrollment tables, join legend</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="25" t="inlineStr"/>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr"/>
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>[Q3 / Q4 (build design)]  docs/Part 3/Program Spec/studypoppage_validated.csv — ELIG_COH, MM_baseline_other/Criterion 7, CT_part/Criterion 9</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="25" t="inlineStr"/>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr"/>
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>[Q2 / Q3 / Q4 (existing SQL)]  apr_30_2026/lot1_studyteam_qs.R — POMA-at-1L other-cancer (Q1a), payer (Q1b), clinical-trial (Q1c), journey-example picker (Q3)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="25" t="inlineStr"/>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr"/>
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>[Q1 journeys]  jun_21_2026/engine/ (run_engine.R, map/lot1/sct/lot_end/lot_long.R), engine/fixtures/expected/TRACE.md, jun_21_2026/README.md</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="25" t="inlineStr"/>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr"/>
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>[Q1 journeys (reproduce)]  Questions/July 5 2026/patient_journey_examples/ — committed inputs, engine outputs, generator + README (one-command reproduce)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="25" t="inlineStr"/>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr"/>
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>[Questions]  Questions/July 5 2026/questiond jul 5.pdf — the source chat</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="B19" s="40" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="26" t="inlineStr"/>
+      <c r="B18" s="40" t="inlineStr">
+        <is>
+          <t>[This workbook (reproducible)]  Questions/July 5 2026/build_workbook.py — regenerates this .xlsx from the committed journey bundle (openpyxl); no hidden state</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>Prepared 2026-07-05. Counts flagged 'needs warehouse run' should be executed against the live cohort before sharing figures externally; this workbook fixes the method and the queries, not the final numbers.</t>
         </is>
@@ -1258,9 +1304,9 @@
     <mergeCell ref="B4"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B9"/>
-    <mergeCell ref="B18"/>
     <mergeCell ref="B7"/>
     <mergeCell ref="B6"/>
+    <mergeCell ref="B20"/>
     <mergeCell ref="B10"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="B5"/>
@@ -1300,150 +1346,150 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9" t="inlineStr"/>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr"/>
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Short answer</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Trace patients raw claims → LOT (LOT1-5, SCT/CAR-T, consolidation)</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Done end-to-end. Six worked journeys on the 'Q1 …' tabs show every step with dates. Real-patient traces use the same MAP_STACKED + LOT_LONG extraction (SQL provided).</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Worked (synthetic); SQL for real patients</t>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Done end-to-end on six SYNTHETIC archetype patients (the 'Q1 …' tabs show every step with dates). These prove the format and the algorithm's behaviour; REAL patient examples run the same MAP_STACKED + LOT_LONG extraction against the warehouse (SQL provided).</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Synthetic worked examples; real = warehouse run</t>
         </is>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>POMA-1L patients who also get SCT or CAR-T = not treatment-naive?</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Partly. An AUTOLOGOUS SCT after 1L is NORMAL first-line care and is NOT evidence of prior treatment. ALLOGENEIC SCT or CAR-T near 1L IS a red flag. Query breaks POMA-1L down by transplant type.</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Needs warehouse run (SQL provided)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Is POMA associated with permissible (other) cancers in baseline?</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Answerable in the ELIG_COH build, which deliberately KEEPS patients flagged for another cancer. Measure the POMA-1L vs non-POMA rate of OTHER_MALIGN_FLAG. An existing script already counts it.</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Needs warehouse run (SQL exists)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Do POMA patients have clinical-trial evidence?</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Answerable in ELIG_COH (clinical-trial patients are also kept). Measure CLINTRIAL_BASELINE / _FOLLOWUP among POMA-1L. Existing script already computes it.</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Needs warehouse run (SQL exists)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Do POMA patients have continuous pharmacy benefit (not just medical)?</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Concern is largely closed by design: every Optum member has BOTH benefits, and baseline MM-therapy (incl. oral LEN/THAL by NDC) is already an exclusion. Residual = exposure before the 6-month look-back only.</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Validated + confirmatory SQL</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Side</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Does Optum track medical &amp; pharmacy coverage separately?</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>You are essentially correct — Optum CDM requires BOTH benefits for membership and tracks coverage as one enrollment span, not two separable streams. Full validation on the 'Optum coverage' tab.</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Validated against docs</t>
         </is>
@@ -1473,7 +1519,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Validation: does Optum separate medical &amp; pharmacy coverage?</t>
         </is>
@@ -1487,14 +1533,14 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Bottom line:  you are essentially correct.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="100" customHeight="1">
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>In Optum CDM, medical and pharmacy are not two separately-enrollable coverages you can hold one of without the other: membership requires BOTH benefits, so there is no 'medical-only, no pharmacy' sub-population, and a member's coverage is modelled as a single continuous-enrollment span rather than as independent medical and pharmacy eligibility records. (The enrollment record does carry a product / plan-type attribute — so Optum is not 'benefit-blind' — but it is one record per member, not two benefit-eligibility tables.) This is why the question keeps recurring: the program spec repeats the phrase 'medical AND pharmacy benefits', which reads as if the two were separable — but in this cohort they move together.</t>
         </is>
@@ -1504,49 +1550,49 @@
       <c r="B6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>The evidence</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>1)  Data asset requires both benefits</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Program spec, DATA_SOURCE (validated from protocol): "…Optum Clinformatics Data Mart (CDM)… Membership restricted to individuals with BOTH medical and pharmacy benefits."   [docs/Part 3/Program Spec/studypoppage_validated.csv]</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>2)  Coverage is one enrollment span, not two streams</t>
         </is>
       </c>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Optum business rules: coverage lives in T_MEMBER_ENROLLMENT (one row per member per change, with ELIGEFF/ELIGEND coverage dates) and is rolled up into T_MEMBER_CONTINUOUS_ENROLLMENT (one span per &lt;30-day-gap continuous period). There is a single eligibility span per member — the product/plan type is an attribute of that one record, not two separate medical and pharmacy eligibility tables.   [Apr 18 2026/Optum - Business Rules/optum business rules.pdf]</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>3)  The cohort's own enrollment rule restates 'both'</t>
         </is>
       </c>
     </row>
     <row r="13" ht="76" customHeight="1">
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Inclusion Criterion 5 / CE_b (Baseline Continuous Enrollment): "=1 if patient has six months of continuous enrollment with medical and pharmacy benefits before the index date… gaps of &lt;=30 days are considered continuously enrolled." This 'medical and pharmacy' wording is a restatement of the Optum both-benefits guarantee, not proof the two are separable. (Note: the cohort builds these 6-month spans from the RAW ELIGEFF/ELIGEND records with a &lt;=30-day gap allowance — its own rule, slightly looser than Optum's native &lt;30-day continuous-enrollment rollup table.)   [studypoppage_validated.csv, CE_b / Criterion 5]</t>
         </is>
@@ -1556,7 +1602,7 @@
       <c r="B14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Why this matters for Julia's Q5 (hidden LEN/THAL exposure)</t>
         </is>
@@ -1570,21 +1616,21 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>•  Every member has pharmacy coverage, so oral LEN/THAL fills DO appear as NDC pharmacy claims for anyone in the cohort.</t>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>•  Every member has pharmacy coverage, so an oral LEN/THAL fill is OBSERVABLE as an NDC pharmacy claim for anyone in the cohort (when adjudicated through the plan).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="62" customHeight="1">
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>•  The cohort already EXCLUDES anyone with a baseline MM-therapy claim — medical (HCPCS/CPT) OR pharmacy (NDC) — in the 6 months before index (Exclusion Criterion 3 / MM_bl_agents). LEN and THAL are captured by NDC provided their codes are in the study's MM-therapy code list (Tab 41 / CL_MMA_CODELIST) — which is the intended design — so a baseline oral first-line exposure would have set the flag and excluded the patient.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>⇒  A delivered POMA-1L patient therefore had observable pharmacy coverage in baseline and no MM-therapy claim in that window. The pharmacy blind spot Julia describes does not exist inside the 6-month baseline.</t>
         </is>
@@ -1594,16 +1640,16 @@
       <c r="B20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>The one real limitation (state it plainly)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="76" customHeight="1">
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Exposure EARLIER than the 6-month (183-day) baseline look-back is not evaluated by the baseline scan. That is a look-back-window limitation, not a medical-vs-pharmacy-benefit gap. (Optum claims physically go back to 2007, so earlier fills may exist in the raw data; the limit is the study's fixed 183-day baseline window, not the data.) It can be quantified for POMA-1L patients by (a) measuring their longest continuous pre-index enrollment span, and (b) scanning ALL available pre-index pharmacy history for LEN/THAL NDCs — see the Q5 tab.</t>
+    <row r="22" ht="90" customHeight="1">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Exposure EARLIER than the 6-month (183-day) baseline look-back is not evaluated by the baseline scan. That is a look-back-window limitation, not a medical-vs-pharmacy-benefit gap. (Optum claims physically go back to 2007, so earlier fills may exist in the raw data; the limit is the study's fixed 183-day baseline window, not the data.) It can be quantified for POMA-1L patients by (a) measuring their longest continuous pre-index enrollment span, and (b) scanning ALL available pre-index pharmacy history for LEN/THAL NDCs — see the Q5 tab. Claims data still only captures ADJUDICATED fills whose NDC is on the study code list; manufacturer samples, cash-pay / out-of-plan fills, and any NDC missing from the list are not observable — so 'observable' is the right word, not 'always visible.'</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1657,7 @@
       <c r="B23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>How to say it back to Julia (one line)</t>
         </is>
@@ -1620,7 +1666,7 @@
     <row r="25" ht="62" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>"Optum only enrols members who carry both medical and pharmacy benefits, so there is no medical-only group and oral LEN/THAL fills are always visible as pharmacy claims; combined with the baseline-therapy exclusion, a POMA-1L patient cannot be hiding an observable-window first-line oral agent. The only gap is exposure before the 6-month look-back, which we can measure directly."</t>
+          <t>"Optum only enrols members who carry both medical and pharmacy benefits, so there is no medical-only group and oral LEN/THAL fills are OBSERVABLE as pharmacy claims (when adjudicated and on our code list); combined with the baseline-therapy exclusion, a POMA-1L patient is very unlikely to be hiding an observable-window first-line oral agent. The remaining gaps are exposure before the 6-month look-back and non-adjudicated fills — both measurable or boundable."</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1716,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Q1 — Patient journeys, raw claims → assigned LOT</t>
         </is>
@@ -1684,7 +1730,7 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>How the algorithm turns claims into lines of therapy</t>
         </is>
@@ -1701,91 +1747,91 @@
       <c r="B6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>The six archetypes (why each was chosen)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>9000000101 — POMA in first line (1L)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>A patient whose FIRST-LINE regimen is pomalidomide (POMA) + dexamethasone. Shows how a POMA-1L record is built and why it stands out (POMA is normally a later-line agent). Answers the setup for Q2-Q5.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>9000000102 — Induction triplet + single autologous SCT + maintenance</t>
         </is>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Bortezomib+lenalidomide+dex induction, one autologous stem-cell transplant, then lenalidomide maintenance. This is STANDARD first-line therapy for a transplant-eligible newly-diagnosed patient: the transplant does NOT start a new line and does NOT imply prior treatment.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>9000000103 — Tandem autologous SCT</t>
         </is>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Two planned autologous transplants ~100 days apart (60-180 day rule) with continuous lenalidomide bridging them. Classified as a planned TANDEM within LOT1 - still first line.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>9000000104 — Allogeneic SCT ends the line -&gt; new line</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Induction, then an ALLOGENEIC transplant. Unlike an autologous SCT, an allo transplant ENDS the line (single-day LOT2), and the next therapy becomes LOT3. Allo/CAR-T around an early line is a red flag for non-treatment-naive status.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>9000000105 — CAR-T with consolidation therapy</t>
         </is>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>First line discontinues, then a CAR-T infusion starts a new line; the daratumumab given within the 45-day consolidation window is captured as that line's regimen. Directly illustrates 'consolidation therapy around CAR-T'.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>9000000106 — Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Five sequential drug-based lines over ~3 years (BORT LENA -&gt; DARA POMA -&gt; CARF -&gt; ELOT POMA -&gt; ISAT LENA). Shows how the algorithm advances the line number and assigns end reasons (MED_ADD vs DISCONTINUATION).</t>
         </is>
@@ -1795,7 +1841,7 @@
       <c r="B20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="72" customHeight="1">
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>⚠  These six are illustrative SYNTHETIC patients (reserved ID range 9000000000+), run through the project's actual LOT engine (jun_21_2026/engine) so the journeys are the algorithm's real, rule-faithful output — not hand-drawn. They demonstrate the exact format Julia will get for real patients. The repository holds no real patient data; a real cohort trace runs the same extraction against the warehouse. The inputs, outputs, and a one-command reproduce step are committed next to this workbook in  Questions/July 5 2026/patient_journey_examples/.</t>
         </is>
@@ -1805,14 +1851,14 @@
       <c r="B22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>To pull the same journey for a REAL patient (Databricks SQL)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="174" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>-- 1. Raw pharmacy + medical claims for one patient (chronological)
 SELECT 'pharmacy' src, FILL_DT dt, NDC code, DAYS_SUP FROM &lt;cdm&gt;.t_rx      WHERE PATID = :pid
@@ -1885,7 +1931,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Q1 — Raw claims (input to the algorithm)</t>
         </is>
@@ -1899,2208 +1945,2208 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Archetype</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Claim date</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Claim type</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Drug / SCT</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>9000000101</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>POMA in first line (1L)</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>POMA</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>9000000101</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>POMA in first line (1L)</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>2021-03-05</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>9000000101</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>POMA in first line (1L)</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>2021-03-25</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>POMA</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>9000000101</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>POMA in first line (1L)</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>2021-04-18</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>POMA</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Induction triplet + single autologous SCT + maintenance</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Induction triplet + single autologous SCT + maintenance</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>2021-06-03</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Induction triplet + single autologous SCT + maintenance</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>2021-06-05</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Induction triplet + single autologous SCT + maintenance</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>2021-06-25</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Induction triplet + single autologous SCT + maintenance</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>2021-06-29</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
+      <c r="F13" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Induction triplet + single autologous SCT + maintenance</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>2021-07-19</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Induction triplet + single autologous SCT + maintenance</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>2021-08-15</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>Procedure (SCT)</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>Autologous</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr">
+      <c r="F15" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Induction triplet + single autologous SCT + maintenance</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F16" s="25" t="inlineStr">
+      <c r="F16" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Induction triplet + single autologous SCT + maintenance</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F17" s="25" t="inlineStr">
+      <c r="F17" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Induction triplet + single autologous SCT + maintenance</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F18" s="25" t="inlineStr">
+      <c r="F18" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>2021-01-05</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="F19" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>2021-01-06</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="F20" s="25" t="inlineStr">
+      <c r="F20" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>2021-01-08</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D21" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="F21" s="25" t="inlineStr">
+      <c r="F21" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>2021-01-29</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="F22" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="F23" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>2021-02-22</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F24" s="25" t="inlineStr">
+      <c r="F24" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>2021-03-18</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D25" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F25" s="25" t="inlineStr">
+      <c r="F25" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="26" t="inlineStr">
         <is>
           <t>Procedure (SCT)</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>Autologous</t>
         </is>
       </c>
-      <c r="F26" s="25" t="inlineStr">
+      <c r="F26" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
         <is>
           <t>2021-04-11</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="F27" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>2021-05-05</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F28" s="25" t="inlineStr">
+      <c r="F28" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C29" s="27" t="inlineStr">
         <is>
           <t>2021-05-29</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="F29" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>2021-06-22</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F30" s="25" t="inlineStr">
+      <c r="F30" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="27" t="inlineStr">
         <is>
           <t>2021-07-10</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>Procedure (SCT)</t>
         </is>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>Autologous</t>
         </is>
       </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="F31" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>2021-07-16</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D32" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F32" s="25" t="inlineStr">
+      <c r="F32" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>Tandem autologous SCT</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C33" s="27" t="inlineStr">
         <is>
           <t>2021-08-09</t>
         </is>
       </c>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="D33" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="E33" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F33" s="25" t="inlineStr">
+      <c r="F33" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Allogeneic SCT ends the line -&gt; new line</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="D34" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E34" s="25" t="inlineStr">
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F34" s="25" t="inlineStr">
+      <c r="F34" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>Allogeneic SCT ends the line -&gt; new line</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C35" s="27" t="inlineStr">
         <is>
           <t>2021-03-05</t>
         </is>
       </c>
-      <c r="D35" s="25" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E35" s="27" t="inlineStr">
+      <c r="E35" s="28" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="F35" s="25" t="inlineStr">
+      <c r="F35" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>Allogeneic SCT ends the line -&gt; new line</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>2021-03-10</t>
         </is>
       </c>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="D36" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="F36" s="25" t="inlineStr">
+      <c r="F36" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="24" t="inlineStr">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Allogeneic SCT ends the line -&gt; new line</t>
         </is>
       </c>
-      <c r="C37" s="26" t="inlineStr">
+      <c r="C37" s="27" t="inlineStr">
         <is>
           <t>2021-03-25</t>
         </is>
       </c>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F37" s="25" t="inlineStr">
+      <c r="F37" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>Allogeneic SCT ends the line -&gt; new line</t>
         </is>
       </c>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t>2021-04-15</t>
         </is>
       </c>
-      <c r="D38" s="25" t="inlineStr">
+      <c r="D38" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E38" s="25" t="inlineStr">
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F38" s="25" t="inlineStr">
+      <c r="F38" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B39" s="25" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>Allogeneic SCT ends the line -&gt; new line</t>
         </is>
       </c>
-      <c r="C39" s="26" t="inlineStr">
+      <c r="C39" s="27" t="inlineStr">
         <is>
           <t>2021-04-15</t>
         </is>
       </c>
-      <c r="D39" s="25" t="inlineStr">
+      <c r="D39" s="26" t="inlineStr">
         <is>
           <t>Procedure (SCT)</t>
         </is>
       </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="E39" s="26" t="inlineStr">
         <is>
           <t>Allogenic</t>
         </is>
       </c>
-      <c r="F39" s="25" t="inlineStr">
+      <c r="F39" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B40" s="25" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>Allogeneic SCT ends the line -&gt; new line</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>2021-05-10</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E40" s="25" t="inlineStr">
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F40" s="25" t="inlineStr">
+      <c r="F40" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="A41" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B41" s="25" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>Allogeneic SCT ends the line -&gt; new line</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
+      <c r="C41" s="27" t="inlineStr">
         <is>
           <t>2021-05-15</t>
         </is>
       </c>
-      <c r="D41" s="25" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>DARA</t>
         </is>
       </c>
-      <c r="F41" s="25" t="inlineStr">
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B42" s="25" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>CAR-T with consolidation therapy</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t>2020-01-06</t>
         </is>
       </c>
-      <c r="D42" s="25" t="inlineStr">
+      <c r="D42" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E42" s="25" t="inlineStr">
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F42" s="25" t="inlineStr">
+      <c r="F42" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="A43" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B43" s="25" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>CAR-T with consolidation therapy</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
+      <c r="C43" s="27" t="inlineStr">
         <is>
           <t>2020-01-07</t>
         </is>
       </c>
-      <c r="D43" s="25" t="inlineStr">
+      <c r="D43" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E43" s="27" t="inlineStr">
+      <c r="E43" s="28" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="F43" s="25" t="inlineStr">
+      <c r="F43" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B44" s="25" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>CAR-T with consolidation therapy</t>
         </is>
       </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>2020-01-09</t>
         </is>
       </c>
-      <c r="D44" s="25" t="inlineStr">
+      <c r="D44" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E44" s="25" t="inlineStr">
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="F44" s="25" t="inlineStr">
+      <c r="F44" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B45" s="25" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>CAR-T with consolidation therapy</t>
         </is>
       </c>
-      <c r="C45" s="26" t="inlineStr">
+      <c r="C45" s="27" t="inlineStr">
         <is>
           <t>2020-01-30</t>
         </is>
       </c>
-      <c r="D45" s="25" t="inlineStr">
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="E45" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F45" s="25" t="inlineStr">
+      <c r="F45" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
+      <c r="A46" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B46" s="25" t="inlineStr">
+      <c r="B46" s="26" t="inlineStr">
         <is>
           <t>CAR-T with consolidation therapy</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>2020-02-02</t>
         </is>
       </c>
-      <c r="D46" s="25" t="inlineStr">
+      <c r="D46" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E46" s="25" t="inlineStr">
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="F46" s="25" t="inlineStr">
+      <c r="F46" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="24" t="inlineStr">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B47" s="25" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>CAR-T with consolidation therapy</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="C47" s="27" t="inlineStr">
         <is>
           <t>2020-02-23</t>
         </is>
       </c>
-      <c r="D47" s="25" t="inlineStr">
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="E47" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F47" s="25" t="inlineStr">
+      <c r="F47" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="24" t="inlineStr">
+      <c r="A48" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B48" s="25" t="inlineStr">
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>CAR-T with consolidation therapy</t>
         </is>
       </c>
-      <c r="C48" s="26" t="inlineStr">
+      <c r="C48" s="27" t="inlineStr">
         <is>
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="D48" s="25" t="inlineStr">
+      <c r="D48" s="26" t="inlineStr">
         <is>
           <t>Procedure (SCT)</t>
         </is>
       </c>
-      <c r="E48" s="25" t="inlineStr">
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>CAR-T</t>
         </is>
       </c>
-      <c r="F48" s="25" t="inlineStr">
+      <c r="F48" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B49" s="25" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>CAR-T with consolidation therapy</t>
         </is>
       </c>
-      <c r="C49" s="26" t="inlineStr">
+      <c r="C49" s="27" t="inlineStr">
         <is>
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="D49" s="25" t="inlineStr">
+      <c r="D49" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="E49" s="26" t="inlineStr">
         <is>
           <t>DARA</t>
         </is>
       </c>
-      <c r="F49" s="25" t="inlineStr">
+      <c r="F49" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
+      <c r="A50" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B50" s="25" t="inlineStr">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C50" s="26" t="inlineStr">
+      <c r="C50" s="27" t="inlineStr">
         <is>
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="D50" s="25" t="inlineStr">
+      <c r="D50" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E50" s="25" t="inlineStr">
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="F50" s="25" t="inlineStr">
+      <c r="F50" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="24" t="inlineStr">
+      <c r="A51" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B51" s="25" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C51" s="26" t="inlineStr">
+      <c r="C51" s="27" t="inlineStr">
         <is>
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="D51" s="25" t="inlineStr">
+      <c r="D51" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="E51" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F51" s="25" t="inlineStr">
+      <c r="F51" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="24" t="inlineStr">
+      <c r="A52" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B52" s="25" t="inlineStr">
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C52" s="26" t="inlineStr">
+      <c r="C52" s="27" t="inlineStr">
         <is>
           <t>2018-06-03</t>
         </is>
       </c>
-      <c r="D52" s="25" t="inlineStr">
+      <c r="D52" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E52" s="27" t="inlineStr">
+      <c r="E52" s="28" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="F52" s="25" t="inlineStr">
+      <c r="F52" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="24" t="inlineStr">
+      <c r="A53" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B53" s="25" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C53" s="26" t="inlineStr">
+      <c r="C53" s="27" t="inlineStr">
         <is>
           <t>2018-06-25</t>
         </is>
       </c>
-      <c r="D53" s="25" t="inlineStr">
+      <c r="D53" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="E53" s="26" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="F53" s="25" t="inlineStr">
+      <c r="F53" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
+      <c r="A54" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B54" s="25" t="inlineStr">
+      <c r="B54" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C54" s="26" t="inlineStr">
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>2018-06-25</t>
         </is>
       </c>
-      <c r="D54" s="25" t="inlineStr">
+      <c r="D54" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E54" s="25" t="inlineStr">
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F54" s="25" t="inlineStr">
+      <c r="F54" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="24" t="inlineStr">
+      <c r="A55" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B55" s="25" t="inlineStr">
+      <c r="B55" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C55" s="26" t="inlineStr">
+      <c r="C55" s="27" t="inlineStr">
         <is>
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="D55" s="25" t="inlineStr">
+      <c r="D55" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="E55" s="26" t="inlineStr">
         <is>
           <t>DARA</t>
         </is>
       </c>
-      <c r="F55" s="25" t="inlineStr">
+      <c r="F55" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A56" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B56" s="25" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C56" s="26" t="inlineStr">
+      <c r="C56" s="27" t="inlineStr">
         <is>
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="D56" s="25" t="inlineStr">
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E56" s="25" t="inlineStr">
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>POMA</t>
         </is>
       </c>
-      <c r="F56" s="25" t="inlineStr">
+      <c r="F56" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="A57" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B57" s="25" t="inlineStr">
+      <c r="B57" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C57" s="26" t="inlineStr">
+      <c r="C57" s="27" t="inlineStr">
         <is>
           <t>2019-02-03</t>
         </is>
       </c>
-      <c r="D57" s="25" t="inlineStr">
+      <c r="D57" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E57" s="27" t="inlineStr">
+      <c r="E57" s="28" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="F57" s="25" t="inlineStr">
+      <c r="F57" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="24" t="inlineStr">
+      <c r="A58" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B58" s="25" t="inlineStr">
+      <c r="B58" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C58" s="26" t="inlineStr">
+      <c r="C58" s="27" t="inlineStr">
         <is>
           <t>2019-02-25</t>
         </is>
       </c>
-      <c r="D58" s="25" t="inlineStr">
+      <c r="D58" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E58" s="25" t="inlineStr">
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>DARA</t>
         </is>
       </c>
-      <c r="F58" s="25" t="inlineStr">
+      <c r="F58" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="24" t="inlineStr">
+      <c r="A59" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B59" s="25" t="inlineStr">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C59" s="26" t="inlineStr">
+      <c r="C59" s="27" t="inlineStr">
         <is>
           <t>2019-02-25</t>
         </is>
       </c>
-      <c r="D59" s="25" t="inlineStr">
+      <c r="D59" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="E59" s="26" t="inlineStr">
         <is>
           <t>POMA</t>
         </is>
       </c>
-      <c r="F59" s="25" t="inlineStr">
+      <c r="F59" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="24" t="inlineStr">
+      <c r="A60" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B60" s="25" t="inlineStr">
+      <c r="B60" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C60" s="26" t="inlineStr">
+      <c r="C60" s="27" t="inlineStr">
         <is>
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="D60" s="25" t="inlineStr">
+      <c r="D60" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E60" s="25" t="inlineStr">
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>CARF</t>
         </is>
       </c>
-      <c r="F60" s="25" t="inlineStr">
+      <c r="F60" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="24" t="inlineStr">
+      <c r="A61" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B61" s="25" t="inlineStr">
+      <c r="B61" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C61" s="26" t="inlineStr">
+      <c r="C61" s="27" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="D61" s="25" t="inlineStr">
+      <c r="D61" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E61" s="27" t="inlineStr">
+      <c r="E61" s="28" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="F61" s="25" t="inlineStr">
+      <c r="F61" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
+      <c r="A62" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B62" s="25" t="inlineStr">
+      <c r="B62" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C62" s="26" t="inlineStr">
+      <c r="C62" s="27" t="inlineStr">
         <is>
           <t>2019-10-25</t>
         </is>
       </c>
-      <c r="D62" s="25" t="inlineStr">
+      <c r="D62" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E62" s="25" t="inlineStr">
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>CARF</t>
         </is>
       </c>
-      <c r="F62" s="25" t="inlineStr">
+      <c r="F62" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="24" t="inlineStr">
+      <c r="A63" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B63" s="25" t="inlineStr">
+      <c r="B63" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C63" s="26" t="inlineStr">
+      <c r="C63" s="27" t="inlineStr">
         <is>
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="D63" s="25" t="inlineStr">
+      <c r="D63" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="E63" s="26" t="inlineStr">
         <is>
           <t>ELOT</t>
         </is>
       </c>
-      <c r="F63" s="25" t="inlineStr">
+      <c r="F63" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="24" t="inlineStr">
+      <c r="A64" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B64" s="25" t="inlineStr">
+      <c r="B64" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C64" s="26" t="inlineStr">
+      <c r="C64" s="27" t="inlineStr">
         <is>
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="D64" s="25" t="inlineStr">
+      <c r="D64" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E64" s="25" t="inlineStr">
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>POMA</t>
         </is>
       </c>
-      <c r="F64" s="25" t="inlineStr">
+      <c r="F64" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="24" t="inlineStr">
+      <c r="A65" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B65" s="25" t="inlineStr">
+      <c r="B65" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C65" s="26" t="inlineStr">
+      <c r="C65" s="27" t="inlineStr">
         <is>
           <t>2020-06-03</t>
         </is>
       </c>
-      <c r="D65" s="25" t="inlineStr">
+      <c r="D65" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E65" s="27" t="inlineStr">
+      <c r="E65" s="28" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="F65" s="25" t="inlineStr">
+      <c r="F65" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="24" t="inlineStr">
+      <c r="A66" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B66" s="25" t="inlineStr">
+      <c r="B66" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C66" s="26" t="inlineStr">
+      <c r="C66" s="27" t="inlineStr">
         <is>
           <t>2020-06-25</t>
         </is>
       </c>
-      <c r="D66" s="25" t="inlineStr">
+      <c r="D66" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E66" s="25" t="inlineStr">
+      <c r="E66" s="26" t="inlineStr">
         <is>
           <t>ELOT</t>
         </is>
       </c>
-      <c r="F66" s="25" t="inlineStr">
+      <c r="F66" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="24" t="inlineStr">
+      <c r="A67" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B67" s="25" t="inlineStr">
+      <c r="B67" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C67" s="26" t="inlineStr">
+      <c r="C67" s="27" t="inlineStr">
         <is>
           <t>2020-06-25</t>
         </is>
       </c>
-      <c r="D67" s="25" t="inlineStr">
+      <c r="D67" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E67" s="25" t="inlineStr">
+      <c r="E67" s="26" t="inlineStr">
         <is>
           <t>POMA</t>
         </is>
       </c>
-      <c r="F67" s="25" t="inlineStr">
+      <c r="F67" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="24" t="inlineStr">
+      <c r="A68" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B68" s="25" t="inlineStr">
+      <c r="B68" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C68" s="26" t="inlineStr">
+      <c r="C68" s="27" t="inlineStr">
         <is>
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="D68" s="25" t="inlineStr">
+      <c r="D68" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E68" s="25" t="inlineStr">
+      <c r="E68" s="26" t="inlineStr">
         <is>
           <t>ISAT</t>
         </is>
       </c>
-      <c r="F68" s="25" t="inlineStr">
+      <c r="F68" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="24" t="inlineStr">
+      <c r="A69" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B69" s="25" t="inlineStr">
+      <c r="B69" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C69" s="26" t="inlineStr">
+      <c r="C69" s="27" t="inlineStr">
         <is>
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="D69" s="25" t="inlineStr">
+      <c r="D69" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E69" s="25" t="inlineStr">
+      <c r="E69" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F69" s="25" t="inlineStr">
+      <c r="F69" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="24" t="inlineStr">
+      <c r="A70" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B70" s="25" t="inlineStr">
+      <c r="B70" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C70" s="26" t="inlineStr">
+      <c r="C70" s="27" t="inlineStr">
         <is>
           <t>2021-02-03</t>
         </is>
       </c>
-      <c r="D70" s="25" t="inlineStr">
+      <c r="D70" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E70" s="27" t="inlineStr">
+      <c r="E70" s="28" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="F70" s="25" t="inlineStr">
+      <c r="F70" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="24" t="inlineStr">
+      <c r="A71" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B71" s="25" t="inlineStr">
+      <c r="B71" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C71" s="26" t="inlineStr">
+      <c r="C71" s="27" t="inlineStr">
         <is>
           <t>2021-02-25</t>
         </is>
       </c>
-      <c r="D71" s="25" t="inlineStr">
+      <c r="D71" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E71" s="25" t="inlineStr">
+      <c r="E71" s="26" t="inlineStr">
         <is>
           <t>ISAT</t>
         </is>
       </c>
-      <c r="F71" s="25" t="inlineStr">
+      <c r="F71" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="24" t="inlineStr">
+      <c r="A72" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B72" s="25" t="inlineStr">
+      <c r="B72" s="26" t="inlineStr">
         <is>
           <t>Deep progressor: LOT1 -&gt; LOT5</t>
         </is>
       </c>
-      <c r="C72" s="26" t="inlineStr">
+      <c r="C72" s="27" t="inlineStr">
         <is>
           <t>2021-02-25</t>
         </is>
       </c>
-      <c r="D72" s="25" t="inlineStr">
+      <c r="D72" s="26" t="inlineStr">
         <is>
           <t>Pharmacy fill</t>
         </is>
       </c>
-      <c r="E72" s="25" t="inlineStr">
+      <c r="E72" s="26" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="F72" s="25" t="inlineStr">
+      <c r="F72" s="26" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
@@ -4135,7 +4181,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Q1 — MAP segments (engine intermediate)</t>
         </is>
@@ -4149,1184 +4195,1184 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Drug</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>MAP #</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>MAP start</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>MAP end</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Discon?</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>9000000101</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>POMA</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>IMID</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>2021-05-29</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>9000000101</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>STEROID</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>2021-03-05</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>2021-04-03</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>IMID</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>STEROID</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>2021-06-03</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>2021-07-02</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>2021-06-05</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>2021-08-03</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>IMID</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>2021-09-15</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>2021-12-13</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr">
+      <c r="G10" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>IMID</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>2021-01-05</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>2021-10-31</t>
         </is>
       </c>
-      <c r="G11" s="28" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>STEROID</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>2021-01-06</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>2021-02-04</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>2021-01-08</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="27" t="inlineStr">
         <is>
           <t>2021-03-08</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr">
+      <c r="G13" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>IMID</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>2021-06-28</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>STEROID</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>2021-03-05</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>2021-04-03</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>2021-03-10</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>2021-04-08</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr">
+      <c r="G16" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>DARA</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>MAB</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>2021-05-15</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="27" t="inlineStr">
         <is>
           <t>2021-06-13</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>IMID</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>2020-01-06</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="27" t="inlineStr">
         <is>
           <t>2020-04-04</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>STEROID</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>2020-01-07</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F19" s="27" t="inlineStr">
         <is>
           <t>2020-02-05</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="G19" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>2020-01-09</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F20" s="27" t="inlineStr">
         <is>
           <t>2020-03-08</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr">
+      <c r="G20" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>DARA</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>MAB</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>2020-09-20</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F21" s="27" t="inlineStr">
         <is>
           <t>2020-10-19</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="G21" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>BORT</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F22" s="27" t="inlineStr">
         <is>
           <t>2018-07-30</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr">
+      <c r="G22" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>IMID</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="F23" s="27" t="inlineStr">
         <is>
           <t>2018-07-30</t>
         </is>
       </c>
-      <c r="G23" s="28" t="inlineStr">
+      <c r="G23" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>STEROID</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>2018-06-03</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F24" s="27" t="inlineStr">
         <is>
           <t>2018-07-02</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr">
+      <c r="G24" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>DARA</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>MAB</t>
         </is>
       </c>
-      <c r="D25" s="26" t="inlineStr">
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" s="26" t="inlineStr">
+      <c r="E25" s="27" t="inlineStr">
         <is>
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="F25" s="26" t="inlineStr">
+      <c r="F25" s="27" t="inlineStr">
         <is>
           <t>2019-04-01</t>
         </is>
       </c>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="G25" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>POMA</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>IMID</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="F26" s="26" t="inlineStr">
+      <c r="F26" s="27" t="inlineStr">
         <is>
           <t>2019-04-01</t>
         </is>
       </c>
-      <c r="G26" s="28" t="inlineStr">
+      <c r="G26" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
         <is>
           <t>STEROID</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E27" s="26" t="inlineStr">
+      <c r="E27" s="27" t="inlineStr">
         <is>
           <t>2019-02-03</t>
         </is>
       </c>
-      <c r="F27" s="26" t="inlineStr">
+      <c r="F27" s="27" t="inlineStr">
         <is>
           <t>2019-03-04</t>
         </is>
       </c>
-      <c r="G27" s="28" t="inlineStr">
+      <c r="G27" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>CARF</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="F28" s="26" t="inlineStr">
+      <c r="F28" s="27" t="inlineStr">
         <is>
           <t>2019-11-29</t>
         </is>
       </c>
-      <c r="G28" s="28" t="inlineStr">
+      <c r="G28" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C29" s="27" t="inlineStr">
         <is>
           <t>STEROID</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E29" s="26" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>2019-10-03</t>
         </is>
       </c>
-      <c r="F29" s="26" t="inlineStr">
+      <c r="F29" s="27" t="inlineStr">
         <is>
           <t>2019-11-01</t>
         </is>
       </c>
-      <c r="G29" s="28" t="inlineStr">
+      <c r="G29" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>ELOT</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>SLAMF7</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="F30" s="27" t="inlineStr">
         <is>
           <t>2020-07-30</t>
         </is>
       </c>
-      <c r="G30" s="28" t="inlineStr">
+      <c r="G30" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>POMA</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="27" t="inlineStr">
         <is>
           <t>IMID</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E31" s="26" t="inlineStr">
+      <c r="E31" s="27" t="inlineStr">
         <is>
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="F31" s="26" t="inlineStr">
+      <c r="F31" s="27" t="inlineStr">
         <is>
           <t>2020-07-30</t>
         </is>
       </c>
-      <c r="G31" s="28" t="inlineStr">
+      <c r="G31" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B32" s="29" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>STEROID</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>2020-06-03</t>
         </is>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="F32" s="27" t="inlineStr">
         <is>
           <t>2020-07-02</t>
         </is>
       </c>
-      <c r="G32" s="28" t="inlineStr">
+      <c r="G32" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>ISAT</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C33" s="27" t="inlineStr">
         <is>
           <t>MAB</t>
         </is>
       </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E33" s="26" t="inlineStr">
+      <c r="E33" s="27" t="inlineStr">
         <is>
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="F33" s="26" t="inlineStr">
+      <c r="F33" s="27" t="inlineStr">
         <is>
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="G33" s="28" t="inlineStr">
+      <c r="G33" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="27" t="inlineStr">
         <is>
           <t>LENA</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>IMID</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="F34" s="26" t="inlineStr">
+      <c r="F34" s="27" t="inlineStr">
         <is>
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="G34" s="28" t="inlineStr">
+      <c r="G34" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>DEX</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C35" s="27" t="inlineStr">
         <is>
           <t>STEROID</t>
         </is>
       </c>
-      <c r="D35" s="26" t="inlineStr">
+      <c r="D35" s="27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E35" s="26" t="inlineStr">
+      <c r="E35" s="27" t="inlineStr">
         <is>
           <t>2021-02-03</t>
         </is>
       </c>
-      <c r="F35" s="26" t="inlineStr">
+      <c r="F35" s="27" t="inlineStr">
         <is>
           <t>2021-03-04</t>
         </is>
       </c>
-      <c r="G35" s="28" t="inlineStr">
+      <c r="G35" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5365,7 +5411,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Q1 — Final LOT assignment (algorithm output)</t>
         </is>
@@ -5379,737 +5425,737 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Patient</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>LOT</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Start type</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Regimen</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>End date</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Length (d)</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>End reason</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>ALLO</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>CAR-T</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>AUTO SCT</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>9000000101</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="27" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>POMA</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>2021-05-29</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="H5" s="30" t="inlineStr">
+      <c r="H5" s="31" t="inlineStr">
         <is>
           <t>DISCONTINUATION</t>
         </is>
       </c>
-      <c r="I5" s="31" t="inlineStr"/>
-      <c r="J5" s="31" t="inlineStr"/>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr"/>
+      <c r="J5" s="32" t="inlineStr"/>
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>9000000102</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>BORT LENA</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>2021-12-13</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="H6" s="30" t="inlineStr">
+      <c r="H6" s="31" t="inlineStr">
         <is>
           <t>DISCONTINUATION</t>
         </is>
       </c>
-      <c r="I6" s="31" t="inlineStr"/>
-      <c r="J6" s="31" t="inlineStr"/>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="I6" s="32" t="inlineStr"/>
+      <c r="J6" s="32" t="inlineStr"/>
+      <c r="K6" s="27" t="inlineStr">
         <is>
           <t>single 2021-08-15</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>9000000103</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>2021-01-05</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>BORT LENA</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>2021-10-31</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="H7" s="30" t="inlineStr">
+      <c r="H7" s="31" t="inlineStr">
         <is>
           <t>DISCONTINUATION</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr"/>
-      <c r="J7" s="31" t="inlineStr"/>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="I7" s="32" t="inlineStr"/>
+      <c r="J7" s="32" t="inlineStr"/>
+      <c r="K7" s="27" t="inlineStr">
         <is>
           <t>tandem 2021-04-01 + 2021-07-10</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>BORT LENA</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>2021-04-14</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H8" s="32" t="inlineStr">
+      <c r="H8" s="33" t="inlineStr">
         <is>
           <t>SCT_ALLO</t>
         </is>
       </c>
-      <c r="I8" s="31" t="inlineStr"/>
-      <c r="J8" s="31" t="inlineStr"/>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr"/>
+      <c r="J8" s="32" t="inlineStr"/>
+      <c r="K8" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>2021-04-15</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>SCT_ALLO</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>(transplant only)</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>2021-04-15</t>
         </is>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H9" s="32" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>SCT_ALLO</t>
         </is>
       </c>
-      <c r="I9" s="31" t="inlineStr">
+      <c r="I9" s="32" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="J9" s="31" t="inlineStr"/>
-      <c r="K9" s="26" t="inlineStr">
+      <c r="J9" s="32" t="inlineStr"/>
+      <c r="K9" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>9000000104</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>2021-05-15</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>DARA</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>2021-06-13</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H10" s="30" t="inlineStr">
+      <c r="H10" s="31" t="inlineStr">
         <is>
           <t>DISCONTINUATION</t>
         </is>
       </c>
-      <c r="I10" s="31" t="inlineStr"/>
-      <c r="J10" s="31" t="inlineStr"/>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr"/>
+      <c r="J10" s="32" t="inlineStr"/>
+      <c r="K10" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>2020-01-06</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>BORT LENA</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>2020-04-04</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="H11" s="30" t="inlineStr">
+      <c r="H11" s="31" t="inlineStr">
         <is>
           <t>DISCONTINUATION</t>
         </is>
       </c>
-      <c r="I11" s="31" t="inlineStr"/>
-      <c r="J11" s="31" t="inlineStr"/>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="I11" s="32" t="inlineStr"/>
+      <c r="J11" s="32" t="inlineStr"/>
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>9000000105</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>CART</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>DARA</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>2020-10-19</t>
         </is>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="H12" s="30" t="inlineStr">
+      <c r="H12" s="31" t="inlineStr">
         <is>
           <t>DISCONTINUATION</t>
         </is>
       </c>
-      <c r="I12" s="31" t="inlineStr"/>
-      <c r="J12" s="31" t="inlineStr">
+      <c r="I12" s="32" t="inlineStr"/>
+      <c r="J12" s="32" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="K12" s="26" t="inlineStr">
+      <c r="K12" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>BORT LENA</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="27" t="inlineStr">
         <is>
           <t>2019-01-31</t>
         </is>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>245</t>
         </is>
       </c>
-      <c r="H13" s="28" t="inlineStr">
+      <c r="H13" s="29" t="inlineStr">
         <is>
           <t>MED_ADD</t>
         </is>
       </c>
-      <c r="I13" s="31" t="inlineStr"/>
-      <c r="J13" s="31" t="inlineStr"/>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="I13" s="32" t="inlineStr"/>
+      <c r="J13" s="32" t="inlineStr"/>
+      <c r="K13" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>DARA POMA</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>2019-09-30</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>242</t>
         </is>
       </c>
-      <c r="H14" s="28" t="inlineStr">
+      <c r="H14" s="29" t="inlineStr">
         <is>
           <t>MED_ADD</t>
         </is>
       </c>
-      <c r="I14" s="31" t="inlineStr"/>
-      <c r="J14" s="31" t="inlineStr"/>
-      <c r="K14" s="26" t="inlineStr">
+      <c r="I14" s="32" t="inlineStr"/>
+      <c r="J14" s="32" t="inlineStr"/>
+      <c r="K14" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>CARF</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>2019-11-29</t>
         </is>
       </c>
-      <c r="G15" s="26" t="inlineStr">
+      <c r="G15" s="27" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H15" s="30" t="inlineStr">
+      <c r="H15" s="31" t="inlineStr">
         <is>
           <t>DISCONTINUATION</t>
         </is>
       </c>
-      <c r="I15" s="31" t="inlineStr"/>
-      <c r="J15" s="31" t="inlineStr"/>
-      <c r="K15" s="26" t="inlineStr">
+      <c r="I15" s="32" t="inlineStr"/>
+      <c r="J15" s="32" t="inlineStr"/>
+      <c r="K15" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>ELOT POMA</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>2020-07-30</t>
         </is>
       </c>
-      <c r="G16" s="26" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H16" s="30" t="inlineStr">
+      <c r="H16" s="31" t="inlineStr">
         <is>
           <t>DISCONTINUATION</t>
         </is>
       </c>
-      <c r="I16" s="31" t="inlineStr"/>
-      <c r="J16" s="31" t="inlineStr"/>
-      <c r="K16" s="26" t="inlineStr">
+      <c r="I16" s="32" t="inlineStr"/>
+      <c r="J16" s="32" t="inlineStr"/>
+      <c r="K16" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>9000000106</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>ISAT LENA</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="27" t="inlineStr">
         <is>
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="G17" s="26" t="inlineStr">
+      <c r="G17" s="27" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H17" s="30" t="inlineStr">
+      <c r="H17" s="31" t="inlineStr">
         <is>
           <t>DISCONTINUATION</t>
         </is>
       </c>
-      <c r="I17" s="31" t="inlineStr"/>
-      <c r="J17" s="31" t="inlineStr"/>
-      <c r="K17" s="26" t="inlineStr">
+      <c r="I17" s="32" t="inlineStr"/>
+      <c r="J17" s="32" t="inlineStr"/>
+      <c r="K17" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Reading the journeys:</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>•  9000000102 (single autologous SCT): the transplant on 2021-08-15 is flagged as an AUTO SCT but does NOT open a new line — LOT1 continues on maintenance to a clean discontinuation. Autologous SCT is part of first line.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>•  9000000104 (allogeneic SCT): the allo transplant ENDS LOT1 (reason SCT_ALLO), creates a single-day LOT2, and the next drug (DARA) becomes LOT3. Allo behaves very differently from auto.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>•  9000000105 (CAR-T + consolidation): after LOT1 discontinues, the CAR-T on 2020-09-01 starts LOT2 and the daratumumab given 19 days later is captured as the CAR-T line's consolidation regimen.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>•  9000000106 (deep progressor): five lines; note two ended by MED_ADD (a new agent added before a full 90-day discontinuation) and three by DISCONTINUATION.</t>
         </is>
@@ -6158,98 +6204,104 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Short answer</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="92" customHeight="1">
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Yes, some POMA-1L patients will have transplant/CAR-T evidence — but it does NOT all point to non-naive status. An AUTOLOGOUS SCT after a first-line regimen is standard care for a transplant-eligible newly-diagnosed patient (induction → auto-SCT → maintenance) and is expected. What genuinely flags a NON-treatment-naive patient is an ALLOGENEIC SCT or a CAR-T infusion at or near first line — those are relapsed/late-line therapies. The query below therefore breaks POMA-1L patients down by transplant TYPE rather than lumping them together.</t>
+    <row r="5" ht="106" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Yes, some POMA-1L patients will have transplant/CAR-T evidence — but it does NOT all point to non-naive status, and WHERE the transplant sits matters. An AUTOLOGOUS SCT at first line is standard care for a transplant-eligible newly-diagnosed patient (induction → auto-SCT → maintenance) and is expected. What flags a NON-treatment-naive patient is an ALLOGENEIC SCT or a CAR-T infusion AT OR CLOSING first line. Critically, allo/CAR-T on a LATER line is NOT a red flag — a genuine POMA-1L patient can progress to CAR-T months later. The query therefore separates 'near 1L' from 'any later line' instead of counting transplant on any line.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="6" customHeight="1">
-      <c r="B6" s="35" t="inlineStr"/>
+      <c r="B6" s="36" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Why this is the right read (clinical framing)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1">
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>• POMA (pomalidomide) is itself normally a relapsed/refractory agent, so POMA appearing in 1L is the anomaly worth investigating — the transplant question is a way of triaging those patients.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>• Autologous SCT → part of first line. Not evidence of prior treatment. (See journey 9000000102 on the Q1 tabs.)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="B10" s="36" t="inlineStr">
-        <is>
-          <t>• Allogeneic SCT or CAR-T near 1L → strong signal the patient had earlier, unobserved lines. (See journeys 9000000104 and 9000000105.)</t>
+    <row r="10" ht="50" customHeight="1">
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>• Allogeneic SCT or CAR-T AT/closing 1L → strong signal of earlier, unobserved lines (journeys 9000000104, 9000000105). The SAME therapy several lines later is expected progression, not a red flag.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="6" customHeight="1">
-      <c r="B11" s="35" t="inlineStr"/>
+      <c r="B11" s="36" t="inlineStr"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t>Query (Databricks) — POMA-1L broken down by transplant type</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="258" customHeight="1">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Query (Databricks) — POMA-1L transplant broken down by WHEN it occurs</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="342" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>WITH poma1l AS (
   SELECT DISTINCT PATID FROM &lt;work&gt;.LOT_LONG
   WHERE LOT_NUM = 1 AND array_contains(split(LOT_BASE_MEDS,' '), 'POMA')
 ),
-flags AS (   -- any transplant/CAR-T evidence on ANY of the patient's lines
+near_1l AS (   -- transplant / CAR-T AT or CLOSING the first line (the 'near 1L' red-flag signal)
   SELECT PATID,
-         max(LOT_TX_AUTO_SING_FLG) auto_single,
-         max(LOT_TX_AUTO_TAND_FLG) auto_tandem,
-         max(LOT_ALLO_LOT_FLG)     allo,
-         max(LOT_CART_LOT_FLG)     cart
+    max(CASE WHEN LOT_NUM=1 AND (LOT_TX_AUTO_SING_FLG=1 OR LOT_TX_AUTO_TAND_FLG=1) THEN 1 ELSE 0 END) auto_1l,
+    max(CASE WHEN (LOT_NUM=1 AND LOT_BASE_END_REASON='SCT_ALLO')
+               OR (LOT_NUM&lt;=2 AND LOT_ALLO_LOT_FLG=1) THEN 1 ELSE 0 END)                              allo_near_1l,
+    max(CASE WHEN (LOT_NUM=1 AND LOT_BASE_END_REASON='SCT_CART')
+               OR (LOT_NUM&lt;=2 AND LOT_CART_LOT_FLG=1) THEN 1 ELSE 0 END)                              cart_near_1l
+  FROM &lt;work&gt;.LOT_LONG GROUP BY PATID
+),
+context AS (   -- allo/CAR-T on ANY line, for context only (does NOT imply non-naive)
+  SELECT PATID, max(LOT_ALLO_LOT_FLG) allo_any, max(LOT_CART_LOT_FLG) cart_any
   FROM &lt;work&gt;.LOT_LONG GROUP BY PATID
 )
-SELECT count(*)                                             AS poma_1l_pts,
-       sum(CASE WHEN auto_single=1 OR auto_tandem=1 THEN 1 END) AS with_autologous_sct,
-       sum(CASE WHEN allo=1 THEN 1 END)                     AS with_allogeneic_sct,
-       sum(CASE WHEN cart=1 THEN 1 END)                     AS with_cart,
-       sum(CASE WHEN allo=1 OR cart=1 THEN 1 END)           AS red_flag_allo_or_cart
-FROM poma1l JOIN flags USING (PATID);</t>
+SELECT count(*)                                                          AS poma_1l_pts,
+       sum(n.auto_1l)                                                    AS autologous_at_1l,   -- normal 1L care
+       sum(n.allo_near_1l)                                               AS allogeneic_near_1l, -- red flag
+       sum(n.cart_near_1l)                                               AS cart_near_1l,       -- red flag
+       sum(CASE WHEN n.allo_near_1l=1 OR n.cart_near_1l=1 THEN 1 ELSE 0 END) AS red_flag_near_1l,
+       sum(CASE WHEN c.allo_any=1  OR c.cart_any=1  THEN 1 ELSE 0 END)   AS allo_or_cart_any_line  -- context only
+FROM poma1l p JOIN near_1l n USING (PATID) JOIN context c USING (PATID);</t>
         </is>
       </c>
     </row>
     <row r="14" ht="6" customHeight="1">
-      <c r="B14" s="35" t="inlineStr"/>
+      <c r="B14" s="36" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Honest limits</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="64" customHeight="1">
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>The strict cohort already removes patients with an OBSERVABLE prior MM therapy (Exclusion Criterion 3). A POMA-1L patient with an allo/CAR-T flag most likely had prior line(s) entirely OUTSIDE the observable window — the transplant evidence is the tell, not a claims error. Pair this count with the pharmacy look-back on the Q5 tab to characterise how much history is unobserved.</t>
+    <row r="16" ht="106" customHeight="1">
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>For the authoritative CAR-T-relative-to-LOT1 timing, use the existing pattern in apr_30_2026/R/validation_qs.R (vqs_q6_cart), which bounds CAR-T to the LOT1 span [LOT1_START, LOT1_END] — extended by one day only when CAR-T closes LOT1 — and reads 'before LOT1' from raw CAR-T claim dates. The LOT_LONG-only query above is a good first pass; vqs_q6_cart is the precise version. Either way, a POMA-1L patient with a near-1L allo/CAR-T most likely had prior line(s) OUTSIDE the observable window (Exclusion Criterion 3 already removes OBSERVABLE prior MM therapy) — the transplant is the tell, not a claims error. Pair with the pharmacy look-back on the Q5 tab.</t>
         </is>
       </c>
     </row>
@@ -6304,48 +6356,48 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>What 'permissible cancers we allow in baseline' means</t>
         </is>
       </c>
     </row>
     <row r="5" ht="92" customHeight="1">
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>The analytic build (ELIG_COH) deliberately does NOT apply Exclusion Criterion 7 (another cancer in baseline). Patients who would normally be excluded for a second cancer are KEPT so the LOT algorithm can run on them and the team can measure exactly this kind of overlap. So 'permissible cancers' = the other-malignancy codes (spec Tab 44) that Criterion 7 would exclude but ELIG_COH retains. There is no separate benign-cancer carve-out list — it is the whole other-malignancy code set, made non-excluding in this build.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="6" customHeight="1">
-      <c r="B6" s="35" t="inlineStr"/>
+      <c r="B6" s="36" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Short answer</t>
         </is>
       </c>
     </row>
     <row r="8" ht="64" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Answerable directly, and the code to count it already exists. Measure the rate of OTHER_MALIGN_FLAG among POMA-1L patients and compare it to non-POMA 1L patients (a relative risk). apr_30_2026/lot1_studyteam_qs.R already computes the POMA-1L other-cancer count (its question Q1a), index-date-aligned, plus a blind-spot quantification.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1">
-      <c r="B9" s="35" t="inlineStr"/>
+      <c r="B9" s="36" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Query (Databricks) — association of POMA-1L with baseline other-cancer</t>
         </is>
       </c>
     </row>
     <row r="11" ht="244" customHeight="1">
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>WITH poma1l AS (
   SELECT DISTINCT cast(PATID AS string) PATID FROM &lt;work&gt;.LOT_LONG
@@ -6359,26 +6411,26 @@
   JOIN &lt;work&gt;.ELIG_COH_FINAL   e ON e.PATID=a.PATID AND e.INDEX_DATE=a.INDEX_DATE
 )
 SELECT CASE WHEN p.PATID IS NOT NULL THEN 'POMA-1L' ELSE 'other-1L' END grp,
-       count(*)                                           AS n_pts,
-       sum(f.OTHER_MALIGN_FLAG)                           AS n_other_cancer,
-       round(100.0*sum(f.OTHER_MALIGN_FLAG)/count(*),1)   AS pct_other_cancer
+       count(*)                                                    AS n_pts,
+       sum(coalesce(f.OTHER_MALIGN_FLAG,0))                        AS n_other_cancer,
+       round(100.0*sum(coalesce(f.OTHER_MALIGN_FLAG,0))/count(*),1) AS pct_other_cancer
 FROM lot1 l JOIN f USING (PATID) LEFT JOIN poma1l p USING (PATID)
 GROUP BY 1;</t>
         </is>
       </c>
     </row>
     <row r="12" ht="6" customHeight="1">
-      <c r="B12" s="35" t="inlineStr"/>
+      <c r="B12" s="36" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Honest limits</t>
         </is>
       </c>
     </row>
     <row r="14" ht="106" customHeight="1">
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Use OTHER_MALIGN_FLAG from ELIG_COH_ALLFLAGS, not a hand-rolled diagnosis query. That flag applies the other-cancer tumour-group codelist (spec Tab 44) with the '&gt;=2 codes on separate days within 30 days for the same tumour type' rule. Note: the protocol also describes a 1-inpatient-or-2-outpatient confirmation, but the pipeline code implements the 30-day-window codelist rule only (no inpatient/outpatient distinction), so treat the flag as codelist-based. A raw ICD-10 C-code scan (e.g. the Kaposi C46* hypothesis) is only a best-effort supplement; lot1_studyteam_qs.R marks it as such.</t>
         </is>

--- a/Questions/July 5 2026/julia_july5_answers.xlsx
+++ b/Questions/July 5 2026/julia_july5_answers.xlsx
@@ -1075,14 +1075,14 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="78" customHeight="1">
+    <row r="9" ht="106" customHeight="1">
       <c r="B9" s="37" t="inlineStr">
         <is>
-          <t>Table names below follow the repo's config_prompts.R: CDM sources are read via cdm_src(), which resolves to the quarterly tables when USE_QUARTERLY_TABLES=TRUE — e.g. cdm_src('rx') → &lt;cdm&gt;.t_rx_2025q2, cdm_src('member_cont_enrollment') → &lt;cdm&gt;.t_member_cont_enrollment_2025q2. LEN/THAL NDCs come from the study's own therapy code list (cl_mma_codelist.csv), the same source the pipeline's mm_therapy_codes view uses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="426" customHeight="1">
+          <t>Table names follow config_prompts.R: CDM sources are read via cdm_src(), which resolves to the quarterly tables when USE_QUARTERLY_TABLES=TRUE (e.g. cdm_src('rx') → &lt;cdm&gt;.t_rx_2025q2). Crucially, this rebuilds CONTINUOUS enrollment spans from RAW member_enrollment with the &lt;=30-day gap rule and keeps only the span that COVERS the index date — exactly as pipeline_steps.R step 13 ('13_enrollment_spans') + step 14 CE do. (Do NOT take min(ELIGEFF)/max(ELIGEND) over all of a patient's rows: that bridges non-continuous coverage and can include post-index spans.) LEN/THAL NDCs come from cl_mma_codelist.csv, the same source as the pipeline's mm_therapy_codes view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="790" customHeight="1">
       <c r="B10" s="24" t="inlineStr">
         <is>
           <t>WITH poma1l AS (
@@ -1090,18 +1090,42 @@
   WHERE LOT_NUM=1 AND array_contains(split(LOT_BASE_MEDS,' '),'POMA')
 ),
 idx AS (SELECT cast(PATID AS string) PATID, INDEX_DATE FROM &lt;work&gt;.ELIG_COH_FINAL),
+-- rebuild continuous enrollment spans from RAW member_enrollment, absorbing &lt;=30-day gaps
+-- (mirrors pipeline_steps.R step 13; gap rule: new span when elig_eff &gt; prev max end + 30 + 1)
+base AS (
+  SELECT cast(PATID AS string) PATID, cast(ELIGEFF AS date) elig_eff, cast(ELIGEND AS date) elig_end
+  FROM &lt;cdm&gt;.t_member_enrollment_2025q2                          -- = cdm_src('member_enrollment')
+  WHERE ELIGEFF IS NOT NULL AND ELIGEND IS NOT NULL
+),
+ordered AS (
+  SELECT *, max(elig_end) OVER (PARTITION BY PATID ORDER BY elig_eff, elig_end
+                                ROWS BETWEEN UNBOUNDED PRECEDING AND 1 PRECEDING) AS max_end_prev
+  FROM base
+),
+flagged AS (
+  SELECT *, CASE WHEN max_end_prev IS NULL THEN 1
+                 WHEN elig_eff &gt; date_add(max_end_prev, 31) THEN 1 ELSE 0 END AS new_grp
+  FROM ordered
+),
+grouped AS (
+  SELECT *, sum(new_grp) OVER (PARTITION BY PATID ORDER BY elig_eff, elig_end
+                               ROWS BETWEEN UNBOUNDED PRECEDING AND CURRENT ROW) AS grp_id
+  FROM flagged
+),
+spans AS (SELECT PATID, grp_id, min(elig_eff) cov_start, max(elig_end) cov_end
+          FROM grouped GROUP BY PATID, grp_id),
+-- the single continuous span that covers each patient's INDEX_DATE
+idx_span AS (
+  SELECT i.PATID, i.INDEX_DATE, s.cov_start
+  FROM idx i JOIN spans s ON s.PATID=i.PATID
+                        AND s.cov_start &lt;= i.INDEX_DATE AND s.cov_end &gt;= i.INDEX_DATE
+),
 -- LEN/THAL NDCs from the study MM-therapy codelist (cl_mma_codelist), 11-digit normalized
 len_thal AS (
   SELECT DISTINCT lpad(regexp_replace(CL_CODE,'[^0-9]',''),11,'0') AS ndc
   FROM &lt;ref&gt;.cl_mma_codelist
   WHERE upper(CL_CODE_TYPE)='NDC' AND upper(CL_MED_ABBR) IN ('LENA','THAL')
 ),
--- longest continuous pre-index enrollment span per patient (proxy for observable history)
-enr AS (
-  SELECT cast(PATID AS string) PATID, min(ELIGEFF) first_cov, max(ELIGEND) last_cov
-  FROM &lt;cdm&gt;.t_member_cont_enrollment_2025q2 GROUP BY PATID     -- = cdm_src('member_cont_enrollment')
-),
--- earliest LEN/THAL pharmacy fill (any time observable)
 early_oral AS (
   SELECT cast(r.PATID AS string) PATID, min(cast(r.FILL_DT AS date)) first_len_thal
   FROM &lt;cdm&gt;.t_rx_2025q2 r                                        -- = cdm_src('rx')
@@ -1109,11 +1133,13 @@
     ON lpad(regexp_replace(coalesce(cast(r.NDC AS string),''),'[^0-9]',''),11,'0') = t.ndc
   GROUP BY r.PATID
 )
-SELECT count(*)                                                            AS poma_1l_pts,
-       sum(CASE WHEN datediff(i.INDEX_DATE, e.first_cov) &gt; 183 THEN 1 ELSE 0 END) AS obs_history_gt_6mo,
-       sum(CASE WHEN o.first_len_thal &lt; date_sub(i.INDEX_DATE,183) THEN 1 ELSE 0 END) AS early_len_thal_pre_baseline
-FROM poma1l p JOIN idx i USING (PATID)
-             JOIN enr e USING (PATID)
+SELECT count(*)                                                                AS poma_1l_pts,
+       -- does the index-covering continuous span reach &gt;183d before index? (room to look back)
+       sum(CASE WHEN datediff(x.INDEX_DATE, x.cov_start) &gt; 183 THEN 1 ELSE 0 END) AS obs_history_gt_6mo,
+       -- LEN/THAL fill inside observable coverage but BEFORE the 6-month baseline window (the true residual)
+       sum(CASE WHEN o.first_len_thal &gt;= x.cov_start
+                 AND o.first_len_thal &lt;  date_sub(x.INDEX_DATE,183) THEN 1 ELSE 0 END) AS early_len_thal_pre_baseline
+FROM poma1l p JOIN idx_span x USING (PATID)
              LEFT JOIN early_oral o USING (PATID);</t>
         </is>
       </c>
@@ -1131,7 +1157,7 @@
     <row r="13" ht="78" customHeight="1">
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>'early_len_thal_pre_baseline' finds prior oral exposure that sits before the 6-month exclusion window — that is exactly the residual blind spot, and it is measurable. What remains truly unobservable is any therapy before a patient's first Optum enrollment date; report obs_history_gt_6mo so Julia can see how many POMA-1L patients even have enough pre-index history for the look-back to be meaningful.</t>
+          <t>'early_len_thal_pre_baseline' finds prior oral exposure that sits inside the patient's index-covering continuous enrollment span but before the 6-month exclusion window — that is exactly the residual blind spot, and it is measurable. What remains truly unobservable is any therapy before that continuous span begins; report obs_history_gt_6mo so Julia can see how many POMA-1L patients even have &gt;6 months of continuous pre-index coverage for the look-back to be meaningful.</t>
         </is>
       </c>
     </row>
@@ -6258,33 +6284,32 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="342" customHeight="1">
+    <row r="13" ht="328" customHeight="1">
       <c r="B13" s="24" t="inlineStr">
         <is>
           <t>WITH poma1l AS (
   SELECT DISTINCT PATID FROM &lt;work&gt;.LOT_LONG
   WHERE LOT_NUM = 1 AND array_contains(split(LOT_BASE_MEDS,' '), 'POMA')
 ),
-near_1l AS (   -- transplant / CAR-T AT or CLOSING the first line (the 'near 1L' red-flag signal)
+first_line AS (   -- the LOT1 row itself: transplant AT / CLOSING the first line
   SELECT PATID,
-    max(CASE WHEN LOT_NUM=1 AND (LOT_TX_AUTO_SING_FLG=1 OR LOT_TX_AUTO_TAND_FLG=1) THEN 1 ELSE 0 END) auto_1l,
-    max(CASE WHEN (LOT_NUM=1 AND LOT_BASE_END_REASON='SCT_ALLO')
-               OR (LOT_NUM&lt;=2 AND LOT_ALLO_LOT_FLG=1) THEN 1 ELSE 0 END)                              allo_near_1l,
-    max(CASE WHEN (LOT_NUM=1 AND LOT_BASE_END_REASON='SCT_CART')
-               OR (LOT_NUM&lt;=2 AND LOT_CART_LOT_FLG=1) THEN 1 ELSE 0 END)                              cart_near_1l
-  FROM &lt;work&gt;.LOT_LONG GROUP BY PATID
+    max(CASE WHEN LOT_TX_AUTO_SING_FLG=1 OR LOT_TX_AUTO_TAND_FLG=1  THEN 1 ELSE 0 END) auto_at_1l,
+    -- CART/ALLO are line-ending in the engine, so 'closed LOT1' == occurred during/closing LOT1
+    max(CASE WHEN LOT_BASE_END_REASON = 'SCT_ALLO'                 THEN 1 ELSE 0 END) allo_closed_1l,
+    max(CASE WHEN LOT_BASE_END_REASON IN ('SCT_CART','CART_INIT')  THEN 1 ELSE 0 END) cart_closed_1l
+  FROM &lt;work&gt;.LOT_LONG WHERE LOT_NUM = 1 GROUP BY PATID
 ),
-context AS (   -- allo/CAR-T on ANY line, for context only (does NOT imply non-naive)
+context AS (   -- allo/CAR-T on ANY line, informational only (later-line progression is expected)
   SELECT PATID, max(LOT_ALLO_LOT_FLG) allo_any, max(LOT_CART_LOT_FLG) cart_any
   FROM &lt;work&gt;.LOT_LONG GROUP BY PATID
 )
-SELECT count(*)                                                          AS poma_1l_pts,
-       sum(n.auto_1l)                                                    AS autologous_at_1l,   -- normal 1L care
-       sum(n.allo_near_1l)                                               AS allogeneic_near_1l, -- red flag
-       sum(n.cart_near_1l)                                               AS cart_near_1l,       -- red flag
-       sum(CASE WHEN n.allo_near_1l=1 OR n.cart_near_1l=1 THEN 1 ELSE 0 END) AS red_flag_near_1l,
-       sum(CASE WHEN c.allo_any=1  OR c.cart_any=1  THEN 1 ELSE 0 END)   AS allo_or_cart_any_line  -- context only
-FROM poma1l p JOIN near_1l n USING (PATID) JOIN context c USING (PATID);</t>
+SELECT count(*)                                                            AS poma_1l_pts,
+       sum(f.auto_at_1l)                                                   AS autologous_at_1l,    -- normal 1L care
+       sum(f.allo_closed_1l)                                               AS allo_closed_1l,      -- red flag
+       sum(f.cart_closed_1l)                                               AS cart_closed_1l,      -- red flag
+       sum(CASE WHEN f.allo_closed_1l=1 OR f.cart_closed_1l=1 THEN 1 ELSE 0 END) AS red_flag_closed_1l,
+       sum(CASE WHEN c.allo_any=1 OR c.cart_any=1 THEN 1 ELSE 0 END)       AS allo_or_cart_any_line  -- context only
+FROM poma1l p JOIN first_line f USING (PATID) JOIN context c USING (PATID);</t>
         </is>
       </c>
     </row>
@@ -6298,10 +6323,10 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="106" customHeight="1">
+    <row r="16" ht="134" customHeight="1">
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>For the authoritative CAR-T-relative-to-LOT1 timing, use the existing pattern in apr_30_2026/R/validation_qs.R (vqs_q6_cart), which bounds CAR-T to the LOT1 span [LOT1_START, LOT1_END] — extended by one day only when CAR-T closes LOT1 — and reads 'before LOT1' from raw CAR-T claim dates. The LOT_LONG-only query above is a good first pass; vqs_q6_cart is the precise version. Either way, a POMA-1L patient with a near-1L allo/CAR-T most likely had prior line(s) OUTSIDE the observable window (Exclusion Criterion 3 already removes OBSERVABLE prior MM therapy) — the transplant is the tell, not a claims error. Pair with the pharmacy look-back on the Q5 tab.</t>
+          <t>The query above uses LOT1's END REASON, which is authoritative for 'CAR-T/allo CLOSED the first line' (CAR-T and allo are line-ending in the engine). It does NOT catch CAR-T that occurred BEFORE first line. For the full, authoritative CAR-T-relative-to-LOT1 breakdown use apr_30_2026/R/validation_qs.R (vqs_q6_cart): it reads FIRST_CART_DT from LOT1_SCT, bounds it to [LOT1_START, LOT1_END] (+1 day only when END_REASON is SCT_CART/CART_INIT), AND reads 'before LOT1' from the raw CAR-T claim dates — the piece LOT_LONG alone cannot give. Either way, a POMA-1L patient with a near-1L allo/CAR-T most likely had prior line(s) OUTSIDE the observable window (Exclusion Criterion 3 removes OBSERVABLE prior MM therapy) — the transplant is the tell, not a claims error. Pair with the pharmacy look-back on the Q5 tab.</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6457,7 @@
     <row r="14" ht="106" customHeight="1">
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Use OTHER_MALIGN_FLAG from ELIG_COH_ALLFLAGS, not a hand-rolled diagnosis query. That flag applies the other-cancer tumour-group codelist (spec Tab 44) with the '&gt;=2 codes on separate days within 30 days for the same tumour type' rule. Note: the protocol also describes a 1-inpatient-or-2-outpatient confirmation, but the pipeline code implements the 30-day-window codelist rule only (no inpatient/outpatient distinction), so treat the flag as codelist-based. A raw ICD-10 C-code scan (e.g. the Kaposi C46* hypothesis) is only a best-effort supplement; lot1_studyteam_qs.R marks it as such.</t>
+          <t>Use OTHER_MALIGN_FLAG from ELIG_COH_ALLFLAGS, not a hand-rolled diagnosis query. That flag applies the other-cancer tumour-group codelist (spec Tab 44) with the protocol confirmation rule: &gt;=1 INPATIENT claim OR &gt;=2 OUTPATIENT claims on separate days within 30 days for the same tumour group — the pipeline classifies inpatient vs outpatient via POS / TOS_CD / confinement (pipeline_steps.R, step 22 '22_other_malig_flag'). A raw ICD-10 C-code scan (e.g. the Kaposi C46* hypothesis) is only a best-effort supplement, not this criterion; lot1_studyteam_qs.R marks its raw scan as such.</t>
         </is>
       </c>
     </row>

--- a/Questions/July 5 2026/julia_july5_answers.xlsx
+++ b/Questions/July 5 2026/julia_july5_answers.xlsx
@@ -766,7 +766,7 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>The five questions (Julia, 4 Jul 2026)</t>
+          <t>The five questions (Julia, chat forwarded — Questions/July 5 2026)</t>
         </is>
       </c>
     </row>
@@ -1883,15 +1883,17 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="174" customHeight="1">
+    <row r="24" ht="202" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>-- 1. Raw pharmacy + medical claims for one patient (chronological)
-SELECT 'pharmacy' src, FILL_DT dt, NDC code, DAYS_SUP FROM &lt;cdm&gt;.t_rx      WHERE PATID = :pid
+          <t>-- CDM tables resolve through cdm_src() to the quarterly names when USE_QUARTERLY_TABLES=TRUE,
+-- e.g. cdm_src('rx') -&gt; &lt;cdm&gt;.t_rx_2025q2, cdm_src('medical') -&gt; &lt;cdm&gt;.t_medical_2025q2.
+-- 1. Raw pharmacy + medical claims for one patient (chronological)
+SELECT 'pharmacy' src, FILL_DT dt, NDC code, DAYS_SUP FROM &lt;cdm&gt;.t_rx_2025q2      WHERE PATID = :pid  -- cdm_src('rx')
 UNION ALL
-SELECT 'medical'  src, FST_DT  dt, PROC_CD, NULL   FROM &lt;cdm&gt;.t_medical    WHERE PATID = :pid
+SELECT 'medical'  src, FST_DT  dt, PROC_CD, NULL   FROM &lt;cdm&gt;.t_medical_2025q2    WHERE PATID = :pid  -- cdm_src('medical')
 ORDER BY dt;
--- 2. The MAP segments the engine built, and the final line assignment
+-- 2. The MAP segments the engine built, and the final line assignment (work schema)
 SELECT * FROM &lt;work&gt;.MAP_STACKED WHERE PATID = :pid ORDER BY MAP_START_DT;
 SELECT LOT_NUM, LOT_START_DT, LOT_START_TYPE, LOT_BASE_MEDS, LOT_BASE_END_DT,
        LOT_BASE_END_REASON, LOT_ALLO_LOT_FLG, LOT_CART_LOT_FLG,

--- a/Questions/July 5 2026/julia_july5_answers.xlsx
+++ b/Questions/July 5 2026/julia_july5_answers.xlsx
@@ -1082,7 +1082,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="790" customHeight="1">
+    <row r="10" ht="888" customHeight="1">
       <c r="B10" s="24" t="inlineStr">
         <is>
           <t>WITH poma1l AS (
@@ -1126,21 +1126,28 @@
   FROM &lt;ref&gt;.cl_mma_codelist
   WHERE upper(CL_CODE_TYPE)='NDC' AND upper(CL_MED_ABBR) IN ('LENA','THAL')
 ),
-early_oral AS (
-  SELECT cast(r.PATID AS string) PATID, min(cast(r.FILL_DT AS date)) first_len_thal
+early_oral AS (   -- ALL LEN/THAL fills (do NOT collapse to min() here; the window filter is applied
+                  --  AFTER joining the index-covering span, so a fill in a PRIOR span can't hide a
+                  --  qualifying pre-baseline fill inside the index span)
+  SELECT cast(r.PATID AS string) PATID, cast(r.FILL_DT AS date) AS fill_dt
   FROM &lt;cdm&gt;.t_rx_2025q2 r                                        -- = cdm_src('rx')
   JOIN len_thal t
     ON lpad(regexp_replace(coalesce(cast(r.NDC AS string),''),'[^0-9]',''),11,'0') = t.ndc
-  GROUP BY r.PATID
+),
+early_flag AS (   -- fills within [cov_start, baseline_start) of the INDEX-COVERING span
+  SELECT x.PATID,
+         max(CASE WHEN o.fill_dt &gt;= x.cov_start
+                   AND o.fill_dt &lt;  date_sub(x.INDEX_DATE,183) THEN 1 ELSE 0 END) AS pre_baseline_len_thal
+  FROM idx_span x LEFT JOIN early_oral o ON o.PATID = x.PATID
+  GROUP BY x.PATID
 )
 SELECT count(*)                                                                AS poma_1l_pts,
        -- does the index-covering continuous span reach &gt;183d before index? (room to look back)
        sum(CASE WHEN datediff(x.INDEX_DATE, x.cov_start) &gt; 183 THEN 1 ELSE 0 END) AS obs_history_gt_6mo,
-       -- LEN/THAL fill inside observable coverage but BEFORE the 6-month baseline window (the true residual)
-       sum(CASE WHEN o.first_len_thal &gt;= x.cov_start
-                 AND o.first_len_thal &lt;  date_sub(x.INDEX_DATE,183) THEN 1 ELSE 0 END) AS early_len_thal_pre_baseline
+       -- any LEN/THAL fill inside observable coverage but BEFORE the 6-month baseline window (the residual)
+       sum(coalesce(ef.pre_baseline_len_thal,0))                              AS early_len_thal_pre_baseline
 FROM poma1l p JOIN idx_span x USING (PATID)
-             LEFT JOIN early_oral o USING (PATID);</t>
+             LEFT JOIN early_flag ef USING (PATID);</t>
         </is>
       </c>
     </row>
@@ -1883,15 +1890,21 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="202" customHeight="1">
+    <row r="24" ht="286" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>-- CDM tables resolve through cdm_src() to the quarterly names when USE_QUARTERLY_TABLES=TRUE,
--- e.g. cdm_src('rx') -&gt; &lt;cdm&gt;.t_rx_2025q2, cdm_src('medical') -&gt; &lt;cdm&gt;.t_medical_2025q2.
--- 1. Raw pharmacy + medical claims for one patient (chronological)
-SELECT 'pharmacy' src, FILL_DT dt, NDC code, DAYS_SUP FROM &lt;cdm&gt;.t_rx_2025q2      WHERE PATID = :pid  -- cdm_src('rx')
-UNION ALL
-SELECT 'medical'  src, FST_DT  dt, PROC_CD, NULL   FROM &lt;cdm&gt;.t_medical_2025q2    WHERE PATID = :pid  -- cdm_src('medical')
+          <t>-- CDM tables resolve through cdm_src() to quarterly names (USE_QUARTERLY_TABLES=TRUE):
+-- cdm_src('rx')-&gt;t_rx_2025q2, ('medical')-&gt;t_medical_2025q2, ('med_procedure')-&gt;t_med_procedure_2025q2,
+-- ('med_diagnosis')-&gt;t_med_diagnosis_2025q2.
+-- 1. ALL raw claim events the algorithm reads, chronological. MM therapy (-&gt; MAP_STACKED) comes from
+--    Rx NDC + medical PROC_CD / BILL_PROC_CD / NDC (pipeline_steps.R step 18); SCT &amp; CAR-T evidence adds
+--    med_procedure.PROC and med_diagnosis.DIAG (validation_qs.R vqs_raw_sct_claims / 02_lot1.R S12).
+SELECT 'rx.NDC'           src, FILL_DT dt, cast(NDC as string)       code FROM &lt;cdm&gt;.t_rx_2025q2          WHERE PATID=:pid
+UNION ALL SELECT 'med.PROC_CD',      FST_DT, cast(PROC_CD as string)      FROM &lt;cdm&gt;.t_medical_2025q2       WHERE PATID=:pid
+UNION ALL SELECT 'med.BILL_PROC_CD', FST_DT, cast(BILL_PROC_CD as string) FROM &lt;cdm&gt;.t_medical_2025q2       WHERE PATID=:pid
+UNION ALL SELECT 'med.NDC',          FST_DT, cast(NDC as string)          FROM &lt;cdm&gt;.t_medical_2025q2       WHERE PATID=:pid
+UNION ALL SELECT 'med_proc.PROC',    FST_DT, cast(PROC as string)         FROM &lt;cdm&gt;.t_med_procedure_2025q2 WHERE PATID=:pid
+UNION ALL SELECT 'dx.DIAG',          FST_DT, cast(DIAG as string)         FROM &lt;cdm&gt;.t_med_diagnosis_2025q2 WHERE PATID=:pid
 ORDER BY dt;
 -- 2. The MAP segments the engine built, and the final line assignment (work schema)
 SELECT * FROM &lt;work&gt;.MAP_STACKED WHERE PATID = :pid ORDER BY MAP_START_DT;
@@ -6269,10 +6282,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="50" customHeight="1">
+    <row r="10" ht="64" customHeight="1">
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>• Allogeneic SCT or CAR-T AT/closing 1L → strong signal of earlier, unobserved lines (journeys 9000000104, 9000000105). The SAME therapy several lines later is expected progression, not a red flag.</t>
+          <t>• Allogeneic SCT or CAR-T that CLOSES 1L → strong signal of earlier, unobserved lines (see 9000000104: the allo transplant ends LOT1). The SAME therapy on a later line is expected progression, NOT a red flag (see 9000000105: LOT1 discontinues, then CAR-T starts LOT2 — this is the 'context only' case, not near-1L).</t>
         </is>
       </c>
     </row>
